--- a/ClosedXML.Tests/Resource/Examples/ConditionalFormatting/CFDataBars.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/ConditionalFormatting/CFDataBars.xlsx
@@ -515,7 +515,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d279bd29-1c16-4e1e-afe3-f09f25236bb6}</x14:id>
+          <x14:id>{eec4d1a7-167c-48aa-90e5-5b9a36862be5}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -529,7 +529,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2286f5e1-34bd-461f-9fa2-230bf1d22276}</x14:id>
+          <x14:id>{e82188dc-c20b-47bb-aaa5-eb9eccff24d0}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -543,7 +543,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e5c9b3e6-d56a-459c-919e-6f617920071f}</x14:id>
+          <x14:id>{dc8d5093-2e00-4d66-96c4-a2936abd0ea8}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -557,7 +557,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bc7a7100-f6a5-43c8-b184-6f80cdfa20c2}</x14:id>
+          <x14:id>{5ed85cce-2633-44e0-a200-04513814e1ee}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -571,7 +571,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9a7bc8ee-1300-46e0-bd57-68b94062871e}</x14:id>
+          <x14:id>{ed616d72-789c-4e30-9775-060eaa19c7c8}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -585,7 +585,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{56343243-5cae-44cd-a87d-e4a64f8bac10}</x14:id>
+          <x14:id>{9fdc881c-9f52-4e83-8072-8f4084a1426c}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -599,7 +599,7 @@
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d279bd29-1c16-4e1e-afe3-f09f25236bb6}">
+          <x14:cfRule type="dataBar" id="{eec4d1a7-167c-48aa-90e5-5b9a36862be5}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -610,7 +610,7 @@
           <xm:sqref>A2:A6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2286f5e1-34bd-461f-9fa2-230bf1d22276}">
+          <x14:cfRule type="dataBar" id="{e82188dc-c20b-47bb-aaa5-eb9eccff24d0}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -625,7 +625,7 @@
           <xm:sqref>B2:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e5c9b3e6-d56a-459c-919e-6f617920071f}">
+          <x14:cfRule type="dataBar" id="{dc8d5093-2e00-4d66-96c4-a2936abd0ea8}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -640,7 +640,7 @@
           <xm:sqref>C2:C6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bc7a7100-f6a5-43c8-b184-6f80cdfa20c2}">
+          <x14:cfRule type="dataBar" id="{5ed85cce-2633-44e0-a200-04513814e1ee}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>50</xm:f>
@@ -655,7 +655,7 @@
           <xm:sqref>D2:D6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9a7bc8ee-1300-46e0-bd57-68b94062871e}">
+          <x14:cfRule type="dataBar" id="{ed616d72-789c-4e30-9775-060eaa19c7c8}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>-SUM($A$2:$E$2)</xm:f>
@@ -670,7 +670,7 @@
           <xm:sqref>E2:E6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{56343243-5cae-44cd-a87d-e4a64f8bac10}">
+          <x14:cfRule type="dataBar" id="{9fdc881c-9f52-4e83-8072-8f4084a1426c}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>30</xm:f>
